--- a/output/pdf_financials_xlsx/API.xlsx
+++ b/output/pdf_financials_xlsx/API.xlsx
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.044319</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.150546</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.013657</v>
       </c>
     </row>
     <row r="104">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.129387</v>
+        <v>0.085068</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.437654</v>
+        <v>0.287108</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.418527</v>
+        <v>0.432184</v>
       </c>
     </row>
     <row r="107">
@@ -3373,7 +3373,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>-0.044319</v>
       </c>
